--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486308_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486308_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5941</v>
+        <v>2.7463</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2472</v>
+        <v>1.8002</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3469</v>
+        <v>0.9462</v>
       </c>
       <c r="G2" t="n">
         <v>1.1153</v>
@@ -610,13 +610,13 @@
         <v>0.6525</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7914</v>
+        <v>0.9436</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9421</v>
+        <v>0.4951</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8492</v>
+        <v>0.4485</v>
       </c>
       <c r="V2" t="n">
         <v>0.0349</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8096</v>
+        <v>1.1352</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4956</v>
+        <v>1.4514</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.686</v>
+        <v>-0.3162</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7575</v>
+        <v>-1.3529</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2619</v>
+        <v>-1.0223</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4956</v>
+        <v>-0.3307</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1802</v>
+        <v>-0.1143</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8797</v>
+        <v>0.4745</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3005</v>
+        <v>-0.5888</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4226</v>
+        <v>-1.2386</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6178</v>
+        <v>-1.4967</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8048999999999999</v>
+        <v>0.2582</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.305</v>
+        <v>-2.3926</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9576</v>
+        <v>2.6101</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8992</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4252</v>
+        <v>0.5684</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.526</v>
+        <v>-0.0277</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4997</v>
+        <v>1.7299</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1952</v>
+        <v>3.3899</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.695</v>
+        <v>-1.6601</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4077</v>
+        <v>1.132</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6006</v>
+        <v>0.2595</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1929</v>
+        <v>0.8724</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3529</v>
+        <v>-4.166</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.0223</v>
+        <v>0.7147</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3307</v>
+        <v>-4.8807</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1143</v>
+        <v>-2.7584</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4745</v>
+        <v>1.6154</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5888</v>
+        <v>-4.3739</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2386</v>
+        <v>-1.4075</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4967</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2582</v>
+        <v>-0.5068</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2175</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.3926</v>
       </c>
       <c r="R4" t="n">
-        <v>2.6101</v>
+        <v>2.3926</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1867</v>
+        <v>0.1782</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2824</v>
+        <v>0.3257</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0956</v>
+        <v>-0.1475</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7299</v>
+        <v>5.1198</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3899</v>
+        <v>5.0849</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6601</v>
+        <v>0.0349</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2305</v>
+        <v>0.9647</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8256</v>
+        <v>2.5582</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.056</v>
+        <v>-1.5935</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7243</v>
+        <v>1.7575</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4807</v>
+        <v>1.2619</v>
       </c>
       <c r="I5" t="n">
-        <v>3.205</v>
+        <v>0.4956</v>
       </c>
       <c r="J5" t="n">
-        <v>4.0775</v>
+        <v>3.1802</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0032</v>
+        <v>1.8797</v>
       </c>
       <c r="L5" t="n">
-        <v>4.0744</v>
+        <v>1.3005</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3532</v>
+        <v>-1.4226</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4838</v>
+        <v>-0.6178</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8694</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>-1.305</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2072</v>
+        <v>0.0544</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0769</v>
+        <v>0.4879</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1303</v>
+        <v>-0.4335</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.6601</v>
+        <v>-1.4997</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.6601</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. COPES</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6538</v>
+        <v>-0.0888</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2548</v>
+        <v>1.7823</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6009</v>
+        <v>-1.8711</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2693</v>
+        <v>2.7243</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.216</v>
+        <v>-0.4807</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4853</v>
+        <v>3.205</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0382</v>
+        <v>4.0775</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.0032</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0382</v>
+        <v>4.0744</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2311</v>
+        <v>-1.3532</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.216</v>
+        <v>-0.4838</v>
       </c>
       <c r="O6" t="n">
-        <v>0.447</v>
+        <v>-0.8694</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.87</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0531</v>
+        <v>-0.0655</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2055</v>
+        <v>-0.1202</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1524</v>
+        <v>0.0547</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.6601</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.6601</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>F. COPES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8593</v>
+        <v>-0.7155</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4986</v>
+        <v>-1.2548</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6393</v>
+        <v>0.5393</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.8108</v>
+        <v>0.2693</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.0929</v>
+        <v>-0.216</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2821</v>
+        <v>0.4853</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.225</v>
+        <v>0.0382</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.378</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.153</v>
+        <v>0.0382</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5858</v>
+        <v>0.2311</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7149</v>
+        <v>-0.216</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1291</v>
+        <v>0.447</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2175</v>
+        <v>-0.87</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1341</v>
+        <v>-0.1148</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6187</v>
+        <v>-0.2055</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5154</v>
+        <v>0.0907</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0349</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1603</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>M. TOWNES VILLAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8633</v>
+        <v>-0.921</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1501</v>
+        <v>-1.5937</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2868</v>
+        <v>0.6727</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.166</v>
+        <v>-0.3571</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7147</v>
+        <v>1.3322</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.8807</v>
+        <v>-1.6893</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.7584</v>
+        <v>1.032</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6154</v>
+        <v>2.2145</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.3739</v>
+        <v>-1.1825</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4075</v>
+        <v>-1.3891</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.8823</v>
       </c>
       <c r="O8" t="n">
         <v>-0.5068</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3926</v>
+        <v>-3.4801</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3926</v>
+        <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8171</v>
+        <v>1.1762</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0839</v>
+        <v>0.8544</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7332</v>
+        <v>0.3217</v>
       </c>
       <c r="V8" t="n">
-        <v>5.1198</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>5.0849</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0349</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. TOWNES VILLAR</t>
+          <t>C. HERMANSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3643</v>
+        <v>-1.6387</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.376</v>
+        <v>-2.7091</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0117</v>
+        <v>1.0704</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3571</v>
+        <v>-2.7475</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3322</v>
+        <v>1.773</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6893</v>
+        <v>-4.5205</v>
       </c>
       <c r="J9" t="n">
-        <v>1.032</v>
+        <v>-2.5577</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2145</v>
+        <v>2.0074</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1825</v>
+        <v>-4.5651</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3891</v>
+        <v>-0.1898</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8823</v>
+        <v>-0.2344</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5068</v>
+        <v>0.0446</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4801</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7329</v>
+        <v>-0.131</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0721</v>
+        <v>-0.1514</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.0204</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4797</v>
+        <v>-1.6655</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4559</v>
+        <v>-1.6109</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0238</v>
+        <v>-0.0546</v>
       </c>
       <c r="G10" t="n">
         <v>-2.7197</v>
@@ -1234,13 +1234,13 @@
         <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>0.805</v>
+        <v>0.6192</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8172</v>
+        <v>0.6621</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0121</v>
+        <v>-0.043</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. HERMANSON</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5385</v>
+        <v>-1.7842</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4856</v>
+        <v>-2.3927</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.6085</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.7475</v>
+        <v>-2.8108</v>
       </c>
       <c r="H11" t="n">
-        <v>1.773</v>
+        <v>-3.0929</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.5205</v>
+        <v>0.2821</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.5577</v>
+        <v>-2.225</v>
       </c>
       <c r="K11" t="n">
-        <v>2.0074</v>
+        <v>-2.378</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.5651</v>
+        <v>0.153</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1898</v>
+        <v>-0.5858</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2344</v>
+        <v>-0.7149</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0446</v>
+        <v>0.1291</v>
       </c>
       <c r="P11" t="n">
-        <v>0.87</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0308</v>
+        <v>1.2092</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0721</v>
+        <v>0.7246</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1029</v>
+        <v>0.4846</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3698</v>
+        <v>0.0349</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3698</v>
+        <v>-0.1603</v>
       </c>
     </row>
     <row r="12">
@@ -1345,31 +1345,31 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.177999999999999</v>
+        <v>-0.835500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.051999999999999</v>
+        <v>-1.7096</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8739999999999999</v>
+        <v>0.8741000000000004</v>
       </c>
       <c r="G12" t="n">
         <v>-8.287600000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6527999999999994</v>
+        <v>0.6527999999999996</v>
       </c>
       <c r="I12" t="n">
-        <v>-8.9406</v>
+        <v>-8.940600000000002</v>
       </c>
       <c r="J12" t="n">
         <v>1.009599999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>7.316300000000002</v>
+        <v>7.3163</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.306699999999999</v>
+        <v>-6.306700000000002</v>
       </c>
       <c r="M12" t="n">
         <v>-9.297000000000001</v>
@@ -1378,7 +1378,7 @@
         <v>-6.6632</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.6338</v>
+        <v>-2.633800000000001</v>
       </c>
       <c r="P12" t="n">
         <v>-1.0876</v>
@@ -1390,10 +1390,10 @@
         <v>14.138</v>
       </c>
       <c r="S12" t="n">
-        <v>4.067699999999999</v>
+        <v>4.410299999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2987</v>
+        <v>3.6411</v>
       </c>
       <c r="U12" t="n">
         <v>0.7688999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8608</v>
+        <v>4.2834</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4101</v>
+        <v>4.7454</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5494</v>
+        <v>-0.462</v>
       </c>
       <c r="G13" t="n">
         <v>7.404</v>
@@ -1468,13 +1468,13 @@
         <v>1.305</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5432</v>
+        <v>-1.1206</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.548</v>
+        <v>-0.2127</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9953</v>
+        <v>-0.9079</v>
       </c>
       <c r="V13" t="n">
         <v>-1.13</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>A. GALAN POZO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3699</v>
+        <v>2.6984</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9229</v>
+        <v>2.0339</v>
       </c>
       <c r="F14" t="n">
-        <v>0.447</v>
+        <v>0.6645</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3974</v>
+        <v>2.6209</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2006</v>
+        <v>-1.9738</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1968</v>
+        <v>4.5947</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3748</v>
+        <v>3.429</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2983</v>
+        <v>-0.7784</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0765</v>
+        <v>4.2074</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7723</v>
+        <v>-0.8082</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4989</v>
+        <v>-1.1954</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2733</v>
+        <v>0.3872</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6525</v>
+        <v>0.6525</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6525</v>
+        <v>1.7401</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3344</v>
+        <v>-0.575</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7677</v>
+        <v>-0.3076</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5667</v>
+        <v>-0.2674</v>
       </c>
       <c r="V14" t="n">
-        <v>2.0854</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.0854</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. GALAN POZO</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2012</v>
+        <v>2.0172</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4751</v>
+        <v>1.6936</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7261</v>
+        <v>0.3237</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6209</v>
+        <v>-0.3974</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.9738</v>
+        <v>-0.2006</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5947</v>
+        <v>-0.1968</v>
       </c>
       <c r="J15" t="n">
-        <v>3.429</v>
+        <v>0.3748</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7784</v>
+        <v>0.2983</v>
       </c>
       <c r="L15" t="n">
-        <v>4.2074</v>
+        <v>0.0765</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8082</v>
+        <v>-0.7723</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1954</v>
+        <v>-0.4989</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3872</v>
+        <v>-0.2733</v>
       </c>
       <c r="P15" t="n">
+        <v>-0.6525</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-1.305</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.6525</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-1.0875</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.7401</v>
-      </c>
       <c r="S15" t="n">
-        <v>-1.0722</v>
+        <v>0.9818</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8663999999999999</v>
+        <v>0.5384</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2057</v>
+        <v>0.4434</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.0854</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.0854</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BARCELLO</t>
+          <t>Y. BARRUETA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2296</v>
+        <v>1.664</v>
       </c>
       <c r="E16" t="n">
-        <v>1.632</v>
+        <v>2.5136</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4024</v>
+        <v>-0.8496</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1867</v>
+        <v>0.4334</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3955</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7913</v>
+        <v>1.2001</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0956</v>
+        <v>1.4425</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9339</v>
+        <v>1.0767</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.0295</v>
+        <v>0.3658</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0911</v>
+        <v>-1.0091</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3293</v>
+        <v>-1.8433</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2382</v>
+        <v>0.8343</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8276</v>
+        <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.041</v>
+        <v>-0.727</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7727000000000001</v>
+        <v>-0.0589</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8137</v>
+        <v>-0.6682</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9347</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2599</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y. BARRUETA</t>
+          <t>A. BARCELLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0449</v>
+        <v>1.0972</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2901</v>
+        <v>1.0732</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2452</v>
+        <v>0.024</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4334</v>
+        <v>-1.1867</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.3955</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2001</v>
+        <v>-0.7913</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4425</v>
+        <v>-0.0956</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0767</v>
+        <v>0.9339</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3658</v>
+        <v>-1.0295</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0091</v>
+        <v>-1.0911</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8433</v>
+        <v>-1.3293</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8343</v>
+        <v>0.2382</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9576</v>
+        <v>2.8276</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3461</v>
+        <v>-0.1733</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2824</v>
+        <v>0.2139</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0638</v>
+        <v>-0.3873</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.9347</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>2.2599</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0861</v>
+        <v>0.2736</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7548</v>
+        <v>-1.5313</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8409</v>
+        <v>1.805</v>
       </c>
       <c r="G18" t="n">
         <v>0.4869</v>
@@ -1858,13 +1858,13 @@
         <v>1.305</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4009</v>
+        <v>-0.2133</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3305</v>
+        <v>-0.1069</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0704</v>
+        <v>-0.1064</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. DE SOUSA ANJO BRITO</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.128</v>
+        <v>-1.0799</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4064</v>
+        <v>-1.9245</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2783</v>
+        <v>0.8446</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1046</v>
+        <v>2.3026</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7039</v>
+        <v>0.5384</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.5993</v>
+        <v>1.7642</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9647</v>
+        <v>1.7323</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7223</v>
+        <v>1.5028</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.687</v>
+        <v>0.2295</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0693</v>
+        <v>0.5704</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0184</v>
+        <v>-0.9643</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0877</v>
+        <v>1.5347</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.305</v>
+        <v>-3.2626</v>
       </c>
       <c r="R19" t="n">
-        <v>1.305</v>
+        <v>2.3926</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2671</v>
+        <v>-1.3826</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2331</v>
+        <v>-0.3941</v>
       </c>
       <c r="U19" t="n">
-        <v>0.034</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4997</v>
+        <v>-1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>-1.13</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>D. DE SOUSA ANJO BRITO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7491</v>
+        <v>-1.6791</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2597</v>
+        <v>-2.7416</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5106000000000001</v>
+        <v>1.0626</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3026</v>
+        <v>0.1046</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5384</v>
+        <v>2.7039</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7642</v>
+        <v>-2.5993</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7323</v>
+        <v>-0.9647</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5028</v>
+        <v>2.7223</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2295</v>
+        <v>-3.687</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5704</v>
+        <v>1.0693</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9643</v>
+        <v>-0.0184</v>
       </c>
       <c r="O20" t="n">
-        <v>1.5347</v>
+        <v>1.0877</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.87</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.2626</v>
+        <v>-1.305</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3926</v>
+        <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.0518</v>
+        <v>-0.2839</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7294</v>
+        <v>-0.1021</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3224</v>
+        <v>-0.1818</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.13</v>
+        <v>-1.4997</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X20" t="n">
         <v>-1.13</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8494</v>
+        <v>-3.6567</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.4713</v>
+        <v>-6.2478</v>
       </c>
       <c r="F21" t="n">
-        <v>2.6219</v>
+        <v>2.5911</v>
       </c>
       <c r="G21" t="n">
         <v>-3.8923</v>
@@ -2092,13 +2092,13 @@
         <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1729</v>
+        <v>0.3656</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3064</v>
+        <v>-0.0829</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4793</v>
+        <v>0.4485</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5649999999999999</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8879</v>
+        <v>-3.6952</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.712</v>
+        <v>-0.4885</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.1759</v>
+        <v>-3.2067</v>
       </c>
       <c r="G22" t="n">
         <v>0.4116</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3871</v>
+        <v>-0.1944</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4795</v>
+        <v>-0.256</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0924</v>
+        <v>0.0616</v>
       </c>
       <c r="V22" t="n">
         <v>-2.8249</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.1781</v>
+        <v>1.922899999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8739999999999999</v>
+        <v>-0.8740000000000003</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0519</v>
+        <v>2.7972</v>
       </c>
       <c r="G23" t="n">
-        <v>8.287599999999999</v>
+        <v>8.287599999999998</v>
       </c>
       <c r="H23" t="n">
         <v>-0.6531</v>
@@ -2227,7 +2227,7 @@
         <v>6.6633</v>
       </c>
       <c r="L23" t="n">
-        <v>2.6338</v>
+        <v>2.633799999999999</v>
       </c>
       <c r="M23" t="n">
         <v>-1.0095</v>
@@ -2248,13 +2248,13 @@
         <v>15.2254</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.0679</v>
+        <v>-3.3227</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7690999999999999</v>
+        <v>-0.7689</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.2989</v>
+        <v>-2.5539</v>
       </c>
       <c r="V23" t="n">
         <v>-4.1295</v>
